--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9025,0.0024,0.0009,0.0913</t>
-  </si>
-  <si>
-    <t>0.0094,0.0003,0.0001,0.9973</t>
-  </si>
-  <si>
-    <t>0.8918,0.0032,0.0003,0.1020</t>
-  </si>
-  <si>
-    <t>0.0406,0.0060,0.0008,0.9842</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0020,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9974,0.0020,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0055,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9966,0.0019,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9471,0.0124,0.0279,0.0019</t>
-  </si>
-  <si>
-    <t>0.0867,0.0035,0.9449,0.0017</t>
-  </si>
-  <si>
-    <t>0.3861,0.0087,0.7270,0.0018</t>
-  </si>
-  <si>
-    <t>0.0806,0.0044,0.9392,0.0026</t>
-  </si>
-  <si>
-    <t>0.9133,0.0233,0.0533,0.0029</t>
-  </si>
-  <si>
-    <t>0.0017,0.9967,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.9926,0.0010,0.0014</t>
-  </si>
-  <si>
-    <t>0.0415,0.9481,0.0151,0.0019</t>
-  </si>
-  <si>
-    <t>0.0133,0.9768,0.0130,0.0023</t>
-  </si>
-  <si>
-    <t>0.0034,0.9944,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.6764,0.0050,0.3835,0.0090</t>
-  </si>
-  <si>
-    <t>0.0820,0.0110,0.9228,0.0090</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9981,0.0024</t>
-  </si>
-  <si>
-    <t>0.0824,0.0669,0.8660,0.0277</t>
-  </si>
-  <si>
-    <t>0.1390,0.0012,0.9415,0.0003</t>
-  </si>
-  <si>
-    <t>0.4549,0.0039,0.6891,0.0049</t>
-  </si>
-  <si>
-    <t>0.0062,0.0009,0.9953,0.0008</t>
-  </si>
-  <si>
-    <t>0.7050,0.4316,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.8642,0.0843,0.0472,0.0011</t>
-  </si>
-  <si>
-    <t>0.0044,0.0297,0.9933,0.0049</t>
-  </si>
-  <si>
-    <t>0.0138,0.9741,0.0149,0.0001</t>
-  </si>
-  <si>
-    <t>0.9252,0.0458,0.0319,0.0066</t>
-  </si>
-  <si>
-    <t>0.9011,0.1199,0.0061,0.0022</t>
-  </si>
-  <si>
-    <t>0.9614,0.0478,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.0028,0.9880,0.3457,0.0016</t>
-  </si>
-  <si>
-    <t>0.0579,0.6196,0.2663,0.0275</t>
-  </si>
-  <si>
-    <t>0.1705,0.0026,0.7507,0.0099</t>
-  </si>
-  <si>
-    <t>0.2678,0.0024,0.8640,0.0013</t>
-  </si>
-  <si>
-    <t>0.0123,0.0015,0.9144,0.0937</t>
-  </si>
-  <si>
-    <t>0.0205,0.1655,0.9697,0.0062</t>
-  </si>
-  <si>
-    <t>0.0032,0.9844,0.0056,0.0028</t>
-  </si>
-  <si>
-    <t>0.0061,0.0100,0.9806,0.0103</t>
-  </si>
-  <si>
-    <t>0.0031,0.7922,0.0031,0.9196</t>
-  </si>
-  <si>
-    <t>0.0084,0.9822,0.0053,0.0033</t>
-  </si>
-  <si>
-    <t>0.0438,0.9257,0.0366,0.0021</t>
-  </si>
-  <si>
-    <t>0.0066,0.9763,0.5276,0.0011</t>
-  </si>
-  <si>
-    <t>0.0042,0.1553,0.9723,0.0065</t>
-  </si>
-  <si>
-    <t>0.0089,0.0317,0.9918,0.0002</t>
-  </si>
-  <si>
-    <t>0.0114,0.0061,0.9854,0.0026</t>
-  </si>
-  <si>
-    <t>0.0182,0.0011,0.9877,0.0016</t>
-  </si>
-  <si>
-    <t>0.0431,0.0226,0.9407,0.0014</t>
-  </si>
-  <si>
-    <t>0.0039,0.0213,0.9871,0.0005</t>
-  </si>
-  <si>
-    <t>0.9898,0.0105,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9837,0.0048,0.0053,0.0019</t>
-  </si>
-  <si>
-    <t>0.9939,0.0022,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.0069,0.3018,0.9797,0.0169</t>
-  </si>
-  <si>
-    <t>0.9952,0.0031,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9975,0.0016,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9944,0.0027,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.8664,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0190,0.9905,0.0033</t>
-  </si>
-  <si>
-    <t>0.0013,0.0087,0.9960,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.9190,0.9548,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0044,0.9969,0.0025</t>
-  </si>
-  <si>
-    <t>0.0183,0.9821,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.0168,0.9842,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7811,0.0142,0.2945,0.0027</t>
-  </si>
-  <si>
-    <t>0.8863,0.0719,0.0474,0.0113</t>
-  </si>
-  <si>
-    <t>0.0035,0.0186,0.9939,0.0041</t>
-  </si>
-  <si>
-    <t>0.0085,0.9315,0.7182,0.0011</t>
-  </si>
-  <si>
-    <t>0.0037,0.9555,0.7739,0.0004</t>
-  </si>
-  <si>
-    <t>0.0044,0.9527,0.0364,0.0156</t>
-  </si>
-  <si>
-    <t>0.0006,0.9854,0.9160,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.0001,0.0002,0.9981</t>
-  </si>
-  <si>
-    <t>0.0005,0.0047,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.0001,0.9991</t>
-  </si>
-  <si>
-    <t>0.0074,0.0018,0.0016,0.9952</t>
-  </si>
-  <si>
-    <t>0.0166,0.0006,0.0009,0.9938</t>
-  </si>
-  <si>
-    <t>0.0011,0.0009,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0029,0.9875,0.2762,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.8712,0.9922,0.0001</t>
-  </si>
-  <si>
-    <t>0.0070,0.7559,0.8447,0.0031</t>
-  </si>
-  <si>
-    <t>0.0020,0.9792,0.1577,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.9099,0.9449,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.9707,0.4880,0.0005</t>
-  </si>
-  <si>
-    <t>0.9946,0.0041,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9836,0.0275,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0010,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0013,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0008,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0037,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0031,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9953,0.0021,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0016,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0033,0.9962,0.0037</t>
-  </si>
-  <si>
-    <t>0.0243,0.0780,0.9503,0.0041</t>
-  </si>
-  <si>
-    <t>0.9768,0.0009,0.0034,0.0056</t>
-  </si>
-  <si>
-    <t>0.0025,0.0015,0.9965,0.0003</t>
-  </si>
-  <si>
-    <t>0.0114,0.9838,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.0036,0.9929,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.0175,0.9787,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0145,0.9830,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.9917,0.0158,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.9974,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7034,0.4105,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.6264,0.2036,0.2132,0.0490</t>
-  </si>
-  <si>
-    <t>0.8497,0.0044,0.2288,0.0012</t>
-  </si>
-  <si>
-    <t>0.8628,0.0184,0.1250,0.0074</t>
-  </si>
-  <si>
-    <t>0.3136,0.0218,0.7320,0.0086</t>
-  </si>
-  <si>
-    <t>0.0292,0.0982,0.0390,0.9485</t>
-  </si>
-  <si>
-    <t>0.0144,0.9863,0.0206,0.0001</t>
-  </si>
-  <si>
-    <t>0.0101,0.9767,0.2270,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.9943,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.0038,0.9671,0.2820,0.0145</t>
-  </si>
-  <si>
-    <t>0.0261,0.9856,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8893,0.0686,0.0435,0.0041</t>
-  </si>
-  <si>
-    <t>0.8503,0.2312,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0006,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.9934,0.0029,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9973,0.0011,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9959,0.0019,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9938,0.0033,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.8972,0.9943,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.4972,0.9637,0.0007</t>
-  </si>
-  <si>
-    <t>0.0089,0.0216,0.9673,0.0041</t>
-  </si>
-  <si>
-    <t>0.0249,0.1509,0.8894,0.0008</t>
-  </si>
-  <si>
-    <t>0.9544,0.0081,0.0184,0.0033</t>
-  </si>
-  <si>
-    <t>0.2314,0.0326,0.7091,0.0660</t>
-  </si>
-  <si>
-    <t>0.7485,0.0005,0.4694,0.0004</t>
-  </si>
-  <si>
-    <t>0.8220,0.0120,0.1984,0.0035</t>
-  </si>
-  <si>
-    <t>0.0186,0.0005,0.0001,0.9961</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0033,0.0028,0.0006,0.9972</t>
-  </si>
-  <si>
-    <t>0.0191,0.0002,0.0001,0.9952</t>
-  </si>
-  <si>
-    <t>0.0031,0.9359,0.9356,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0021,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.1111,0.9082,0.0011,0.0029</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.7037,0.3962,0.0051,0.0021</t>
-  </si>
-  <si>
-    <t>0.9956,0.0004,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.2646,0.0124,0.0029,0.8590</t>
-  </si>
-  <si>
-    <t>0.9965,0.0012,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.5477,0.8899,0.0381</t>
-  </si>
-  <si>
-    <t>0.8926,0.0127,0.0295,0.0542</t>
-  </si>
-  <si>
-    <t>0.9818,0.0032,0.0044,0.0046</t>
-  </si>
-  <si>
-    <t>0.2249,0.7796,0.0155,0.0065</t>
-  </si>
-  <si>
-    <t>0.9839,0.0063,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.9606,0.0170,0.0108,0.0029</t>
-  </si>
-  <si>
-    <t>0.0693,0.9233,0.0057,0.0038</t>
-  </si>
-  <si>
-    <t>0.8147,0.1806,0.0547,0.0126</t>
-  </si>
-  <si>
-    <t>0.9789,0.0104,0.0052,0.0012</t>
-  </si>
-  <si>
-    <t>0.9960,0.0006,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9941,0.0058,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0001,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9956,0.0013,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9964,0.0026,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0017,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9841,0.0204,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.7725,0.3081,0.0058,0.0003</t>
-  </si>
-  <si>
-    <t>0.8224,0.2894,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9284,0.0712,0.0170,0.0056</t>
-  </si>
-  <si>
-    <t>0.9916,0.0085,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9961,0.0017,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9923,0.0094,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9917,0.0060,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.0670,0.9986,0.0012</t>
-  </si>
-  <si>
-    <t>0.9848,0.0112,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.0007,0.0017,0.9975,0.0017</t>
-  </si>
-  <si>
-    <t>0.0039,0.0135,0.9910,0.0013</t>
-  </si>
-  <si>
-    <t>0.0510,0.0062,0.9580,0.0039</t>
-  </si>
-  <si>
-    <t>0.0055,0.0286,0.9879,0.0013</t>
-  </si>
-  <si>
-    <t>0.0013,0.0175,0.9929,0.0032</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9984,0.0009</t>
-  </si>
-  <si>
-    <t>0.0073,0.0144,0.9831,0.0032</t>
-  </si>
-  <si>
-    <t>0.2087,0.0284,0.8100,0.0036</t>
-  </si>
-  <si>
-    <t>0.0191,0.0107,0.9794,0.0038</t>
-  </si>
-  <si>
-    <t>0.8775,0.0089,0.1624,0.0012</t>
-  </si>
-  <si>
-    <t>0.5216,0.0555,0.3835,0.0006</t>
-  </si>
-  <si>
-    <t>0.1304,0.1873,0.6418,0.0013</t>
-  </si>
-  <si>
-    <t>0.8406,0.0038,0.2111,0.0008</t>
-  </si>
-  <si>
-    <t>0.5297,0.0520,0.3465,0.0807</t>
-  </si>
-  <si>
-    <t>0.4921,0.0496,0.5519,0.0088</t>
-  </si>
-  <si>
-    <t>0.8102,0.3277,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0189,0.9775,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9912,0.0085,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9818,0.0232,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.1660,0.8793,0.0027,0.0016</t>
-  </si>
-  <si>
-    <t>0.4442,0.2492,0.3175,0.0283</t>
-  </si>
-  <si>
-    <t>0.9824,0.0011,0.0065,0.0016</t>
-  </si>
-  <si>
-    <t>0.9717,0.0009,0.0102,0.0029</t>
-  </si>
-  <si>
-    <t>0.2415,0.0141,0.8219,0.0045</t>
-  </si>
-  <si>
-    <t>0.9203,0.0013,0.0864,0.0016</t>
-  </si>
-  <si>
-    <t>0.0267,0.0235,0.9486,0.0334</t>
-  </si>
-  <si>
-    <t>0.0113,0.2446,0.9193,0.0129</t>
-  </si>
-  <si>
-    <t>0.0144,0.0415,0.9825,0.0015</t>
-  </si>
-  <si>
-    <t>0.5441,0.0031,0.6295,0.0008</t>
-  </si>
-  <si>
-    <t>0.0144,0.6690,0.7261,0.0052</t>
-  </si>
-  <si>
-    <t>0.9945,0.0014,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9937,0.0059,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9936,0.0062,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9908,0.0060,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9952,0.0025,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9966,0.0007,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.0050,0.0430,0.9823,0.0125</t>
-  </si>
-  <si>
-    <t>0.1847,0.3080,0.6216,0.0049</t>
-  </si>
-  <si>
-    <t>0.9571,0.0046,0.0062,0.0139</t>
-  </si>
-  <si>
-    <t>0.0105,0.0105,0.9892,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0010,0.9943,0.0053</t>
-  </si>
-  <si>
-    <t>0.0224,0.2367,0.9258,0.0049</t>
-  </si>
-  <si>
-    <t>0.0022,0.0032,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0177,0.0375,0.9489,0.0052</t>
-  </si>
-  <si>
-    <t>0.0033,0.0062,0.9937,0.0013</t>
-  </si>
-  <si>
-    <t>0.0147,0.0046,0.9797,0.0028</t>
-  </si>
-  <si>
-    <t>0.0223,0.0591,0.9287,0.0119</t>
-  </si>
-  <si>
-    <t>0.7989,0.0170,0.1515,0.0269</t>
-  </si>
-  <si>
-    <t>0.9156,0.0015,0.0639,0.0059</t>
-  </si>
-  <si>
-    <t>0.9931,0.0006,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9920,0.0069,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9963,0.0012,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9967,0.0017,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0052,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0002,0.0002,0.0026</t>
-  </si>
-  <si>
-    <t>0.9961,0.0016,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9968,0.0029,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0201,0.2059,0.7679,0.0038</t>
-  </si>
-  <si>
-    <t>0.0052,0.0199,0.9882,0.0009</t>
-  </si>
-  <si>
-    <t>0.0165,0.0180,0.9634,0.0046</t>
-  </si>
-  <si>
-    <t>0.0522,0.0044,0.9472,0.0111</t>
-  </si>
-  <si>
-    <t>0.0087,0.0022,0.9938,0.0003</t>
-  </si>
-  <si>
-    <t>0.3300,0.0068,0.5837,0.0435</t>
-  </si>
-  <si>
-    <t>0.2175,0.0706,0.7016,0.0777</t>
-  </si>
-  <si>
-    <t>0.2931,0.0416,0.2979,0.2864</t>
-  </si>
-  <si>
-    <t>0.9052,0.0012,0.0036,0.1041</t>
-  </si>
-  <si>
-    <t>0.0425,0.0378,0.0003,0.9469</t>
-  </si>
-  <si>
-    <t>0.0218,0.0063,0.0072,0.9816</t>
-  </si>
-  <si>
-    <t>0.0037,0.0001,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.9575,0.0057,0.0060,0.0233</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9518,0.0188,0.0036,0.0114</t>
+  </si>
+  <si>
+    <t>0.0134,0.0003,0.0001,0.9965</t>
+  </si>
+  <si>
+    <t>0.8893,0.0058,0.0003,0.0674</t>
+  </si>
+  <si>
+    <t>0.0161,0.0019,0.0004,0.9942</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9866,0.0124,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9960,0.0023,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9268,0.0189,0.0399,0.0014</t>
+  </si>
+  <si>
+    <t>0.2914,0.0445,0.6429,0.0031</t>
+  </si>
+  <si>
+    <t>0.8296,0.0034,0.3014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0603,0.0130,0.9364,0.0042</t>
+  </si>
+  <si>
+    <t>0.9146,0.0148,0.0554,0.0051</t>
+  </si>
+  <si>
+    <t>0.0018,0.9963,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9926,0.0037,0.0008</t>
+  </si>
+  <si>
+    <t>0.1359,0.8858,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.0108,0.9839,0.0063,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.9982,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.6214,0.0015,0.4119,0.0078</t>
+  </si>
+  <si>
+    <t>0.8564,0.0013,0.2006,0.0007</t>
+  </si>
+  <si>
+    <t>0.0073,0.0009,0.9913,0.0011</t>
+  </si>
+  <si>
+    <t>0.0324,0.0105,0.9576,0.0066</t>
+  </si>
+  <si>
+    <t>0.0874,0.0008,0.9654,0.0003</t>
+  </si>
+  <si>
+    <t>0.0617,0.0018,0.9617,0.0023</t>
+  </si>
+  <si>
+    <t>0.0058,0.0015,0.9955,0.0007</t>
+  </si>
+  <si>
+    <t>0.2883,0.7774,0.0101,0.0006</t>
+  </si>
+  <si>
+    <t>0.7574,0.1250,0.1477,0.0048</t>
+  </si>
+  <si>
+    <t>0.0094,0.0216,0.9810,0.0171</t>
+  </si>
+  <si>
+    <t>0.0059,0.9480,0.2225,0.0002</t>
+  </si>
+  <si>
+    <t>0.6863,0.3349,0.1044,0.0154</t>
+  </si>
+  <si>
+    <t>0.8434,0.0481,0.0810,0.0037</t>
+  </si>
+  <si>
+    <t>0.1728,0.8730,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.0106,0.9708,0.2452,0.0012</t>
+  </si>
+  <si>
+    <t>0.0149,0.8016,0.1708,0.0089</t>
+  </si>
+  <si>
+    <t>0.0428,0.0115,0.9249,0.0167</t>
+  </si>
+  <si>
+    <t>0.0077,0.0067,0.9869,0.0026</t>
+  </si>
+  <si>
+    <t>0.0448,0.0008,0.9566,0.0028</t>
+  </si>
+  <si>
+    <t>0.0088,0.1251,0.9797,0.0020</t>
+  </si>
+  <si>
+    <t>0.0061,0.9817,0.0096,0.0008</t>
+  </si>
+  <si>
+    <t>0.0126,0.0650,0.9668,0.0040</t>
+  </si>
+  <si>
+    <t>0.1364,0.6381,0.0403,0.3019</t>
+  </si>
+  <si>
+    <t>0.0083,0.9678,0.0370,0.0321</t>
+  </si>
+  <si>
+    <t>0.0138,0.9772,0.0094,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.9914,0.0592,0.0067</t>
+  </si>
+  <si>
+    <t>0.0137,0.0823,0.9590,0.0035</t>
+  </si>
+  <si>
+    <t>0.0009,0.4762,0.9928,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.0018,0.9869,0.0150</t>
+  </si>
+  <si>
+    <t>0.0071,0.0010,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0252,0.0097,0.9745,0.0013</t>
+  </si>
+  <si>
+    <t>0.0077,0.0950,0.9642,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0022,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9832,0.0052,0.0028,0.0047</t>
+  </si>
+  <si>
+    <t>0.9959,0.0015,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.1490,0.9918,0.0540</t>
+  </si>
+  <si>
+    <t>0.9913,0.0083,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0013,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.7344,0.9799,0.0007</t>
+  </si>
+  <si>
+    <t>0.0037,0.0374,0.9868,0.0065</t>
+  </si>
+  <si>
+    <t>0.0009,0.0030,0.9974,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9570,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.0029,0.9949,0.0003</t>
+  </si>
+  <si>
+    <t>0.0121,0.9849,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9957,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.6748,0.0182,0.4171,0.0056</t>
+  </si>
+  <si>
+    <t>0.9530,0.0536,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.0081,0.0427,0.9863,0.0044</t>
+  </si>
+  <si>
+    <t>0.0019,0.9076,0.8780,0.0004</t>
+  </si>
+  <si>
+    <t>0.0022,0.7440,0.9709,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.9907,0.0256,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.9888,0.1240,0.0047</t>
+  </si>
+  <si>
+    <t>0.0058,0.0004,0.0043,0.9940</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0034,0.0004,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.0036,0.0029,0.0008,0.9963</t>
+  </si>
+  <si>
+    <t>0.0115,0.0006,0.0002,0.9958</t>
+  </si>
+  <si>
+    <t>0.0105,0.9397,0.5670,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.9755,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0136,0.3546,0.7618,0.0082</t>
+  </si>
+  <si>
+    <t>0.0053,0.8802,0.8677,0.0011</t>
+  </si>
+  <si>
+    <t>0.0037,0.9322,0.8576,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.9555,0.5539,0.0012</t>
+  </si>
+  <si>
+    <t>0.9967,0.0023,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0026,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0011,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9887,0.0153,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9915,0.0107,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0081,0.0031,0.9874,0.0098</t>
+  </si>
+  <si>
+    <t>0.1297,0.0400,0.8783,0.0019</t>
+  </si>
+  <si>
+    <t>0.8628,0.0036,0.0547,0.0270</t>
+  </si>
+  <si>
+    <t>0.0114,0.0029,0.9882,0.0034</t>
+  </si>
+  <si>
+    <t>0.0061,0.9890,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.9950,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0130,0.9804,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.0027,0.9942,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9945,0.0042,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.9949,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.1199,0.9060,0.0029,0.0005</t>
+  </si>
+  <si>
+    <t>0.2593,0.1527,0.6570,0.0713</t>
+  </si>
+  <si>
+    <t>0.5893,0.0015,0.5462,0.0026</t>
+  </si>
+  <si>
+    <t>0.7077,0.0069,0.2902,0.0169</t>
+  </si>
+  <si>
+    <t>0.0474,0.0209,0.9427,0.0039</t>
+  </si>
+  <si>
+    <t>0.0048,0.1536,0.0048,0.9799</t>
+  </si>
+  <si>
+    <t>0.0089,0.9837,0.1179,0.0006</t>
+  </si>
+  <si>
+    <t>0.0081,0.9865,0.0160,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.9873,0.0077,0.0270</t>
+  </si>
+  <si>
+    <t>0.0014,0.9818,0.2403,0.0120</t>
+  </si>
+  <si>
+    <t>0.0133,0.9826,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.8689,0.1494,0.0150,0.0010</t>
+  </si>
+  <si>
+    <t>0.9535,0.0602,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9930,0.0021,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9968,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0712,0.9897,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.7780,0.9430,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.0204,0.9835,0.0017</t>
+  </si>
+  <si>
+    <t>0.0153,0.0229,0.9707,0.0022</t>
+  </si>
+  <si>
+    <t>0.9670,0.0022,0.0159,0.0026</t>
+  </si>
+  <si>
+    <t>0.2383,0.0138,0.7617,0.0190</t>
+  </si>
+  <si>
+    <t>0.9806,0.0003,0.0221,0.0002</t>
+  </si>
+  <si>
+    <t>0.2695,0.1268,0.6405,0.0089</t>
+  </si>
+  <si>
+    <t>0.0225,0.0014,0.0007,0.9915</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0116,0.0005,0.0001,0.9964</t>
+  </si>
+  <si>
+    <t>0.0022,0.9740,0.6293,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.0334,0.9556,0.0017,0.0057</t>
+  </si>
+  <si>
+    <t>0.9870,0.0047,0.0015,0.0031</t>
+  </si>
+  <si>
+    <t>0.7627,0.3147,0.0062,0.0016</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9002,0.0044,0.0036,0.1232</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0058,0.2882,0.9120,0.0410</t>
+  </si>
+  <si>
+    <t>0.9648,0.0017,0.0033,0.0264</t>
+  </si>
+  <si>
+    <t>0.9698,0.0035,0.0071,0.0132</t>
+  </si>
+  <si>
+    <t>0.1504,0.8448,0.0172,0.0059</t>
+  </si>
+  <si>
+    <t>0.9796,0.0029,0.0060,0.0023</t>
+  </si>
+  <si>
+    <t>0.9203,0.0192,0.0500,0.0043</t>
+  </si>
+  <si>
+    <t>0.5781,0.4295,0.0086,0.0064</t>
+  </si>
+  <si>
+    <t>0.5461,0.3605,0.2230,0.0284</t>
+  </si>
+  <si>
+    <t>0.9502,0.0326,0.0101,0.0036</t>
+  </si>
+  <si>
+    <t>0.9945,0.0018,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9955,0.0019,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0010,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0006,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.8884,0.1296,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.8620,0.1954,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.9272,0.0752,0.0103,0.0019</t>
+  </si>
+  <si>
+    <t>0.2315,0.1706,0.7440,0.0070</t>
+  </si>
+  <si>
+    <t>0.9953,0.0017,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9884,0.0024,0.0005,0.0043</t>
+  </si>
+  <si>
+    <t>0.9973,0.0017,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9719,0.0290,0.0030,0.0013</t>
+  </si>
+  <si>
+    <t>0.0036,0.0273,0.9958,0.0008</t>
+  </si>
+  <si>
+    <t>0.9841,0.0261,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0019,0.9962,0.0007</t>
+  </si>
+  <si>
+    <t>0.0022,0.0226,0.9923,0.0030</t>
+  </si>
+  <si>
+    <t>0.0098,0.0060,0.9858,0.0045</t>
+  </si>
+  <si>
+    <t>0.0045,0.0520,0.9856,0.0011</t>
+  </si>
+  <si>
+    <t>0.0065,0.0059,0.9890,0.0024</t>
+  </si>
+  <si>
+    <t>0.0087,0.0002,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0055,0.9925,0.0034</t>
+  </si>
+  <si>
+    <t>0.1139,0.0362,0.8147,0.0683</t>
+  </si>
+  <si>
+    <t>0.5810,0.0115,0.4978,0.0060</t>
+  </si>
+  <si>
+    <t>0.1085,0.0364,0.8536,0.0036</t>
+  </si>
+  <si>
+    <t>0.0700,0.5142,0.4813,0.0063</t>
+  </si>
+  <si>
+    <t>0.0269,0.0882,0.8933,0.0036</t>
+  </si>
+  <si>
+    <t>0.6967,0.0105,0.3689,0.0009</t>
+  </si>
+  <si>
+    <t>0.6710,0.0565,0.2843,0.0231</t>
+  </si>
+  <si>
+    <t>0.5834,0.1890,0.2894,0.0112</t>
+  </si>
+  <si>
+    <t>0.2864,0.8607,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1367,0.9070,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.9777,0.0263,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9549,0.0823,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.5821,0.5840,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9018,0.0410,0.0427,0.0016</t>
+  </si>
+  <si>
+    <t>0.9761,0.0028,0.0107,0.0011</t>
+  </si>
+  <si>
+    <t>0.9353,0.0038,0.0111,0.0216</t>
+  </si>
+  <si>
+    <t>0.7825,0.0144,0.2432,0.0038</t>
+  </si>
+  <si>
+    <t>0.8701,0.0091,0.1502,0.0027</t>
+  </si>
+  <si>
+    <t>0.0077,0.0065,0.9796,0.0569</t>
+  </si>
+  <si>
+    <t>0.0183,0.0359,0.9568,0.0077</t>
+  </si>
+  <si>
+    <t>0.0286,0.0195,0.9337,0.0124</t>
+  </si>
+  <si>
+    <t>0.3097,0.0044,0.8564,0.0003</t>
+  </si>
+  <si>
+    <t>0.0355,0.0871,0.9359,0.0058</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0048,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0062,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0068,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0079,0.1112,0.9852,0.0060</t>
+  </si>
+  <si>
+    <t>0.0503,0.3953,0.7404,0.0055</t>
+  </si>
+  <si>
+    <t>0.8899,0.0045,0.0820,0.0069</t>
+  </si>
+  <si>
+    <t>0.0165,0.0109,0.9814,0.0012</t>
+  </si>
+  <si>
+    <t>0.0035,0.0020,0.9905,0.0028</t>
+  </si>
+  <si>
+    <t>0.0126,0.2171,0.9017,0.0007</t>
+  </si>
+  <si>
+    <t>0.0071,0.0074,0.9937,0.0007</t>
+  </si>
+  <si>
+    <t>0.0031,0.0026,0.9932,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0139,0.9808,0.0013</t>
+  </si>
+  <si>
+    <t>0.0031,0.0057,0.9917,0.0021</t>
+  </si>
+  <si>
+    <t>0.9723,0.0028,0.0130,0.0008</t>
+  </si>
+  <si>
+    <t>0.7675,0.0129,0.2015,0.0187</t>
+  </si>
+  <si>
+    <t>0.9630,0.0057,0.0167,0.0023</t>
+  </si>
+  <si>
+    <t>0.9884,0.0104,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9954,0.0010,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9972,0.0015,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0046,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.9961,0.0025,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0277,0.0883,0.8974,0.0061</t>
+  </si>
+  <si>
+    <t>0.0068,0.0630,0.9829,0.0019</t>
+  </si>
+  <si>
+    <t>0.0111,0.0203,0.9760,0.0053</t>
+  </si>
+  <si>
+    <t>0.0078,0.0079,0.9877,0.0014</t>
+  </si>
+  <si>
+    <t>0.0193,0.0029,0.9862,0.0002</t>
+  </si>
+  <si>
+    <t>0.0526,0.0037,0.8824,0.0825</t>
+  </si>
+  <si>
+    <t>0.0810,0.0127,0.9412,0.0017</t>
+  </si>
+  <si>
+    <t>0.4046,0.0182,0.5704,0.0499</t>
+  </si>
+  <si>
+    <t>0.9059,0.0009,0.0213,0.0271</t>
+  </si>
+  <si>
+    <t>0.0596,0.0095,0.0026,0.9689</t>
+  </si>
+  <si>
+    <t>0.0182,0.0033,0.0007,0.9923</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.9722,0.0027,0.0033,0.0150</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2617,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2995,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3093,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4115,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
